--- a/outputs/chip-report/台股盤後籌碼_2026-09-09.xlsx
+++ b/outputs/chip-report/台股盤後籌碼_2026-09-09.xlsx
@@ -578,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N126"/>
+  <dimension ref="A1:N132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2011,7 +2011,7 @@
       <c r="F110" s="6" t="n"/>
       <c r="G110" s="6" t="n"/>
       <c r="I110" s="6" t="n">
-        <v>52.2</v>
+        <v>54.4</v>
       </c>
       <c r="J110" s="6" t="n"/>
       <c r="K110" s="6" t="n"/>
@@ -2079,7 +2079,7 @@
       <c r="G115" s="15" t="n"/>
       <c r="I115" s="15" t="inlineStr">
         <is>
-          <t>微台多空比位階(45日)</t>
+          <t>散戶多單持倉占比位階(45日)</t>
         </is>
       </c>
       <c r="J115" s="15" t="n"/>
@@ -2097,7 +2097,7 @@
       <c r="F116" s="6" t="n"/>
       <c r="G116" s="6" t="n"/>
       <c r="I116" s="6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="J116" s="6" t="n"/>
       <c r="K116" s="6" t="n"/>
@@ -2147,19 +2147,80 @@
       <c r="J119" s="7" t="n"/>
       <c r="K119" s="7" t="n"/>
     </row>
+    <row r="121">
+      <c r="A121" s="16" t="inlineStr">
+        <is>
+          <t>【CROWDING】
+散戶空單持倉占比位階(45日)</t>
+        </is>
+      </c>
+      <c r="B121" s="16" t="n"/>
+      <c r="C121" s="16" t="n"/>
+      <c r="E121" s="15" t="inlineStr">
+        <is>
+          <t>微台多空比位階(45日)</t>
+        </is>
+      </c>
+      <c r="F121" s="15" t="n"/>
+      <c r="G121" s="15" t="n"/>
+    </row>
     <row r="122">
-      <c r="A122" s="19" t="inlineStr">
+      <c r="A122" s="17" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="B122" s="17" t="n"/>
+      <c r="C122" s="17" t="n"/>
+      <c r="E122" s="6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F122" s="6" t="n"/>
+      <c r="G122" s="6" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="17" t="n"/>
+      <c r="B123" s="17" t="n"/>
+      <c r="C123" s="17" t="n"/>
+      <c r="E123" s="6" t="n"/>
+      <c r="F123" s="6" t="n"/>
+      <c r="G123" s="6" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="18" t="inlineStr">
+        <is>
+          <t>近45日相對位階（同值取中間排名）= (低於本日筆數 + 同值筆數 / 2) / 樣本數 x 100。 小台＋微台等值口數；微台 5 口換算為 1 口小台等值。；目前樣本 45 筆。</t>
+        </is>
+      </c>
+      <c r="B124" s="18" t="n"/>
+      <c r="C124" s="18" t="n"/>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>近45日相對位階（同值取中間排名）= (低於本日筆數 + 同值筆數 / 2) / 樣本數 x 100。 小台＋微台等值口數；微台 5 口換算為 1 口小台等值。；目前樣本 45 筆。</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="n"/>
+      <c r="G124" s="7" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="18" t="n"/>
+      <c r="B125" s="18" t="n"/>
+      <c r="C125" s="18" t="n"/>
+      <c r="E125" s="7" t="n"/>
+      <c r="F125" s="7" t="n"/>
+      <c r="G125" s="7" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="19" t="inlineStr">
         <is>
           <t>這是 2026-09-09 的盤後籌碼正式版：加權指數收 47,183.36 點、漲 77.58 點，盤中最高 47,548.26 點、最低 47,060.78 點，成交值約 8,159.77 億元；TWSE 信用交易統計已補回，融資金額餘額 5,871.67 億、較前一交易日增加 9.00 億，融券餘額 203,610 張、較前一交易日減少 5,004 張。TAIFEX 的外資(大小台)期貨未平倉依原表合併口徑 = TXF + MXF/4 + TMF/20，9/9 約為 -79,711，與結算比約 2,102、與前日增減約 2,245；主表 OP 欄位維持 BC-SC 與 BP-SP 的淨額口徑。</t>
         </is>
       </c>
     </row>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
   </sheetData>
-  <mergeCells count="158">
+  <mergeCells count="164">
     <mergeCell ref="E116:G117"/>
     <mergeCell ref="I103:K103"/>
     <mergeCell ref="E13:G13"/>
@@ -2178,6 +2239,7 @@
     <mergeCell ref="E48:G49"/>
     <mergeCell ref="A91:C91"/>
     <mergeCell ref="I104:K105"/>
+    <mergeCell ref="A128:N132"/>
     <mergeCell ref="A16:C17"/>
     <mergeCell ref="I26:K27"/>
     <mergeCell ref="I106:K107"/>
@@ -2185,6 +2247,7 @@
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="E74:G75"/>
     <mergeCell ref="A83:C83"/>
+    <mergeCell ref="E121:G121"/>
     <mergeCell ref="I68:K69"/>
     <mergeCell ref="A86:C87"/>
     <mergeCell ref="I58:K59"/>
@@ -2207,8 +2270,10 @@
     <mergeCell ref="A110:C111"/>
     <mergeCell ref="A48:C49"/>
     <mergeCell ref="A97:C97"/>
+    <mergeCell ref="E122:G123"/>
     <mergeCell ref="E78:G79"/>
     <mergeCell ref="I51:K51"/>
+    <mergeCell ref="A121:C121"/>
     <mergeCell ref="A54:C55"/>
     <mergeCell ref="I72:K73"/>
     <mergeCell ref="A13:C13"/>
@@ -2233,11 +2298,11 @@
     <mergeCell ref="I25:K25"/>
     <mergeCell ref="I98:K99"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A122:N126"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="E26:G27"/>
     <mergeCell ref="A68:C69"/>
     <mergeCell ref="E66:G67"/>
+    <mergeCell ref="E124:G125"/>
     <mergeCell ref="E106:G107"/>
     <mergeCell ref="E65:G65"/>
     <mergeCell ref="A52:C53"/>
@@ -2271,6 +2336,7 @@
     <mergeCell ref="I57:K57"/>
     <mergeCell ref="I48:K49"/>
     <mergeCell ref="A104:C105"/>
+    <mergeCell ref="A122:C123"/>
     <mergeCell ref="E80:G81"/>
     <mergeCell ref="E51:G51"/>
     <mergeCell ref="E16:G17"/>
@@ -2297,6 +2363,7 @@
     <mergeCell ref="A115:C115"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A66:C67"/>
+    <mergeCell ref="A124:C125"/>
     <mergeCell ref="I22:K23"/>
     <mergeCell ref="I28:K29"/>
     <mergeCell ref="A118:C119"/>
